--- a/KAMCHATKA_ZAPOLNENIE/03_ООО_Торговый_Дом_АДЛ.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/03_ООО_Торговый_Дом_АДЛ.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -103,6 +103,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -485,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -598,7 +601,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+          <t>Графы марка / производитель / страна / № записи частично ПРЕДЗАПОЛНЕНЫ нами по вашему КП и открытым данным — проверьте и исправьте, если не так.</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -632,287 +635,212 @@
       <c r="AD3" s="2" t="n"/>
       <c r="AE3" s="2" t="n"/>
     </row>
-    <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
+      <c r="AA4" s="2" t="n"/>
+      <c r="AB4" s="2" t="n"/>
+      <c r="AC4" s="2" t="n"/>
+      <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Табл./№ ТЗ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ГОСТ/ТУ</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Ду, мм</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Проход</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Давление, МПа</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Температура, °С</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Среда</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Материал корпуса</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Климатическое исполнение</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Присоединение</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: наименование</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: технические характеристики</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Установочное положение</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Материал штока, шара, уплотнений</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Габариты</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Предлагаемая марка / обозначение</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Производитель (завод)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Страна происхождения</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>№ реестровой записи (ПП 719) или евразийского реестра</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Срок действия записи</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Соответствие ТЗ: «да» или отличия</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Цена за ед. с НДС, ₽</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>Сумма с НДС, ₽</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Срок отгрузки</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD5" s="4" t="inlineStr">
         <is>
           <t>Вес ед., кг / габариты</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>Сертификат / декларация ТР ТС №</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>1.3/154</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 100, Ру 16</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>ТУ 3700-001-81673229-2007</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>стандарт</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>-20…+110</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>вода</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Серый чугун EN-GJL-250</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Класс герметичности: А</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>межфланцевый</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Ручной</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Ручка с фиксацией произвольного положения</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>Корпус: Серый чугун GG25 Седло: EPDM Диск: Нержавеющая сталь CF8M</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="9">
-        <f>AA5*S5</f>
-        <v/>
-      </c>
-      <c r="AC5" s="7" t="n"/>
-      <c r="AD5" s="7" t="n"/>
-      <c r="AE5" s="7" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1.3/155</t>
+          <t>1.3/154</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 100 Ру 16</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 100, Ру 16</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -937,78 +865,106 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>до +115°C (кратковременно до +130°C)</t>
+          <t>-20…+110</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>вода (в том числе питьевая), растворы гликоля до 45%, горячий воздух, прочие нейтральные среды</t>
+          <t>вода</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr"/>
+          <t>Серый чугун EN-GJL-250</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Класс герметичности: А</t>
+        </is>
+      </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>межфланцевое</t>
+          <t>межфланцевый</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>ручной (рукоятка)</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="6" t="inlineStr"/>
+          <t>Ручной</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>Ручка с фиксацией произвольного положения</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Седло- EPDM HT; Диск - Нержавеющая сталь CF8M</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr"/>
+          <t>Корпус: Серый чугун GG25 Седло: EPDM Диск: Нержавеющая сталь CF8M</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S6" s="5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="n"/>
-      <c r="AA6" s="8" t="n"/>
-      <c r="AB6" s="9">
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПВС FL(w)-3-100-MR-E Ду100 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X6" s="8" t="n"/>
+      <c r="Y6" s="8" t="n"/>
+      <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="10">
         <f>AA6*S6</f>
         <v/>
       </c>
-      <c r="AC6" s="7" t="n"/>
-      <c r="AD6" s="7" t="n"/>
-      <c r="AE6" s="7" t="n"/>
+      <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="n"/>
+      <c r="AE6" s="8" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1.3/156</t>
+          <t>1.3/155</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 150 Ру 16</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 100 Ру 16</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1018,7 +974,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1071,40 +1027,52 @@
         </is>
       </c>
       <c r="S7" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="7" t="n"/>
-      <c r="X7" s="7" t="n"/>
-      <c r="Y7" s="7" t="n"/>
-      <c r="Z7" s="7" t="n"/>
-      <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="9">
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПТЛ FLN(w)-5-100-MR-HT Ду100 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="10">
         <f>AA7*S7</f>
         <v/>
       </c>
-      <c r="AC7" s="7" t="n"/>
-      <c r="AD7" s="7" t="n"/>
-      <c r="AE7" s="7" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>1.3/157</t>
+          <t>1.3/156</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 200 Ру 16</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 150 Ру 16</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1114,7 +1082,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1167,40 +1135,52 @@
         </is>
       </c>
       <c r="S8" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="9">
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПТЛ FLN(w)-5-150-MR-HT Ду150 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="10">
         <f>AA8*S8</f>
         <v/>
       </c>
-      <c r="AC8" s="7" t="n"/>
-      <c r="AD8" s="7" t="n"/>
-      <c r="AE8" s="7" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>1.3/158</t>
+          <t>1.3/157</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 80 Ру 16</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 200 Ру 16</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1210,7 +1190,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1259,44 +1239,56 @@
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M38936</t>
+          <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
         </is>
       </c>
       <c r="S9" s="5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
-      <c r="Z9" s="7" t="n"/>
-      <c r="AA9" s="8" t="n"/>
-      <c r="AB9" s="9">
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПТЛ FLN(w)-5-200-MR-HT Ду200 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X9" s="8" t="n"/>
+      <c r="Y9" s="8" t="n"/>
+      <c r="Z9" s="8" t="n"/>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="10">
         <f>AA9*S9</f>
         <v/>
       </c>
-      <c r="AC9" s="7" t="n"/>
-      <c r="AD9" s="7" t="n"/>
-      <c r="AE9" s="7" t="n"/>
+      <c r="AC9" s="8" t="n"/>
+      <c r="AD9" s="8" t="n"/>
+      <c r="AE9" s="8" t="n"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>1.3/159</t>
+          <t>1.3/158</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 150 Ру 16</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 80 Ру 16</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1306,7 +1298,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1321,94 +1313,90 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>-20…+110</t>
+          <t>до +115°C (кратковременно до +130°C)</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>вода</t>
+          <t>вода (в том числе питьевая), растворы гликоля до 45%, горячий воздух, прочие нейтральные среды</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Серый чугун EN-GJL-250</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>Класс герметичности: А</t>
-        </is>
-      </c>
+          <t>Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>межфланцевый</t>
+          <t>межфланцевое</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>Ручной</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>Ручка с фиксацией произвольного положения</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>ручной (рукоятка)</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr"/>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Корпус: Серый чугун GG25 Седло: EPDM Диск: Нержавеющая сталь CF8M</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Седло- EPDM HT; Диск - Нержавеющая сталь CF8M</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M38936</t>
         </is>
       </c>
       <c r="S10" s="5" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U10" s="7" t="n"/>
-      <c r="V10" s="7" t="n"/>
-      <c r="W10" s="7" t="n"/>
-      <c r="X10" s="7" t="n"/>
-      <c r="Y10" s="7" t="n"/>
-      <c r="Z10" s="7" t="n"/>
-      <c r="AA10" s="8" t="n"/>
-      <c r="AB10" s="9">
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПТЛ FLN(w)-5-080-MR-HT Ду80 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="10">
         <f>AA10*S10</f>
         <v/>
       </c>
-      <c r="AC10" s="7" t="n"/>
-      <c r="AD10" s="7" t="n"/>
-      <c r="AE10" s="7" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>1.3/160</t>
+          <t>1.3/159</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 200 Ру 16</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 150 Ру 16</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1418,7 +1406,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1487,40 +1475,52 @@
         </is>
       </c>
       <c r="S11" s="5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U11" s="7" t="n"/>
-      <c r="V11" s="7" t="n"/>
-      <c r="W11" s="7" t="n"/>
-      <c r="X11" s="7" t="n"/>
-      <c r="Y11" s="7" t="n"/>
-      <c r="Z11" s="7" t="n"/>
-      <c r="AA11" s="8" t="n"/>
-      <c r="AB11" s="9">
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПВС FL(w)-3-150-MR-E Ду150 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="10">
         <f>AA11*S11</f>
         <v/>
       </c>
-      <c r="AC11" s="7" t="n"/>
-      <c r="AD11" s="7" t="n"/>
-      <c r="AE11" s="7" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1.3/161</t>
+          <t>1.3/160</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 80</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 200 Ру 16</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1599,40 +1599,52 @@
         </is>
       </c>
       <c r="S12" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U12" s="7" t="n"/>
-      <c r="V12" s="7" t="n"/>
-      <c r="W12" s="7" t="n"/>
-      <c r="X12" s="7" t="n"/>
-      <c r="Y12" s="7" t="n"/>
-      <c r="Z12" s="7" t="n"/>
-      <c r="AA12" s="8" t="n"/>
-      <c r="AB12" s="9">
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПВС FL(w)-3-200-MR-E Ду200 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="n"/>
+      <c r="Y12" s="8" t="n"/>
+      <c r="Z12" s="8" t="n"/>
+      <c r="AA12" s="9" t="n"/>
+      <c r="AB12" s="10">
         <f>AA12*S12</f>
         <v/>
       </c>
-      <c r="AC12" s="7" t="n"/>
-      <c r="AD12" s="7" t="n"/>
-      <c r="AE12" s="7" t="n"/>
+      <c r="AC12" s="8" t="n"/>
+      <c r="AD12" s="8" t="n"/>
+      <c r="AE12" s="8" t="n"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>1.3/162</t>
+          <t>1.3/161</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Затвор поворотный дисковый Ду 65 Ру 16  ГРАНВЭЛ тип ЗПВС</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 80</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1642,7 +1654,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1657,47 +1669,47 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>-20…+112</t>
+          <t>-20…+110</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Вода</t>
+          <t>вода</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>чугун</t>
+          <t>Серый чугун EN-GJL-250</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>У1</t>
+          <t>Класс герметичности: А</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>межфланцовое</t>
+          <t>межфланцевый</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>Ручное</t>
+          <t>Ручной</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>Рукоятка</t>
+          <t>Ручка с фиксацией произвольного положения</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>любое</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Затвор диска поворотный ЗПВС-FL(w)-3150-MR-E, ДУ-65, РУ-16, межфланцовый, рукоятка, корпус-GG25, диск-GGG40, седло -EPDM, Т раб=-15…+110С</t>
+          <t>Корпус: Серый чугун GG25 Седло: EPDM Диск: Нержавеющая сталь CF8M</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
@@ -1705,7 +1717,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr"/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="S13" s="5" t="n">
         <v>2</v>
       </c>
@@ -1714,96 +1730,228 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U13" s="7" t="n"/>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="7" t="n"/>
-      <c r="X13" s="7" t="n"/>
-      <c r="Y13" s="7" t="n"/>
-      <c r="Z13" s="7" t="n"/>
-      <c r="AA13" s="8" t="n"/>
-      <c r="AB13" s="9">
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПВС FL(w)-3-080-MR-E Ду80 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="10">
         <f>AA13*S13</f>
         <v/>
       </c>
-      <c r="AC13" s="7" t="n"/>
-      <c r="AD13" s="7" t="n"/>
-      <c r="AE13" s="7" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>1.3/162</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Затвор поворотный дисковый Ду 65 Ру 16  ГРАНВЭЛ тип ЗПВС</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>ТУ 3700-001-81673229-2007</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>-20…+112</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Вода</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>чугун</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>У1</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>межфланцовое</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Ручное</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>Рукоятка</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Затвор диска поворотный ЗПВС-FL(w)-3150-MR-E, ДУ-65, РУ-16, межфланцовый, рукоятка, корпус-GG25, диск-GGG40, седло -EPDM, Т раб=-15…+110С</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПВС FL(w)-3-065-MR-E Ду65 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="10">
+        <f>AA14*S14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>1.6/11</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Клапан предохранительный 17с11нж Ду 25 Ру 16</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>ТУ 3742-005-22294686-2009</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>стандарт</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>От -40 до +225</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>Вода, воздух, пар, аммиак, нефть, жидкие углеводороды и нефтепродукты, масляные фракции и другие, среды, в которых скорость коррозии материала корпуса не превышает 0,2мм в год</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>Углеродистая сталь</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>У</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>Штуцерно-торцевое</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N14" s="6" t="inlineStr">
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O14" s="6" t="inlineStr">
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>Наименование
 Клапан предохранительный
@@ -1830,110 +1978,6 @@
 Предназначенная для защиты от механического разрушения оборудования и трубопроводов избыточным давлением путём автоматического выпуска избытка рабочей среды</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr"/>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="U14" s="7" t="n"/>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="7" t="n"/>
-      <c r="X14" s="7" t="n"/>
-      <c r="Y14" s="7" t="n"/>
-      <c r="Z14" s="7" t="n"/>
-      <c r="AA14" s="8" t="n"/>
-      <c r="AB14" s="9">
-        <f>AA14*S14</f>
-        <v/>
-      </c>
-      <c r="AC14" s="7" t="n"/>
-      <c r="AD14" s="7" t="n"/>
-      <c r="AE14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>1.6/89</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 100, Ру 16</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>стандарт</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>до + 110 °С</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>теплоснабжение, горячий воздух (до 12 бар), питьевая горячая вода.</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>серый чугун GG25</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>У</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>межфланцевый</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>любое</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
-        </is>
-      </c>
       <c r="Q15" s="6" t="inlineStr"/>
       <c r="R15" s="6" t="inlineStr"/>
       <c r="S15" s="5" t="n">
@@ -1944,33 +1988,33 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U15" s="7" t="n"/>
-      <c r="V15" s="7" t="n"/>
-      <c r="W15" s="7" t="n"/>
-      <c r="X15" s="7" t="n"/>
-      <c r="Y15" s="7" t="n"/>
-      <c r="Z15" s="7" t="n"/>
-      <c r="AA15" s="8" t="n"/>
-      <c r="AB15" s="9">
+      <c r="U15" s="8" t="n"/>
+      <c r="V15" s="8" t="n"/>
+      <c r="W15" s="8" t="n"/>
+      <c r="X15" s="8" t="n"/>
+      <c r="Y15" s="8" t="n"/>
+      <c r="Z15" s="8" t="n"/>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="10">
         <f>AA15*S15</f>
         <v/>
       </c>
-      <c r="AC15" s="7" t="n"/>
-      <c r="AD15" s="7" t="n"/>
-      <c r="AE15" s="7" t="n"/>
+      <c r="AC15" s="8" t="n"/>
+      <c r="AD15" s="8" t="n"/>
+      <c r="AE15" s="8" t="n"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>1.6/90</t>
+          <t>1.6/89</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 80 Ру 16</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 100, Ру 16</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1980,7 +2024,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -2035,51 +2079,63 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M389</t>
+          <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U16" s="7" t="n"/>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="7" t="n"/>
-      <c r="X16" s="7" t="n"/>
-      <c r="Y16" s="7" t="n"/>
-      <c r="Z16" s="7" t="n"/>
-      <c r="AA16" s="8" t="n"/>
-      <c r="AB16" s="9">
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПТЛ FLN(w)-5-100-MR-HT Ду100 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="10">
         <f>AA16*S16</f>
         <v/>
       </c>
-      <c r="AC16" s="7" t="n"/>
-      <c r="AD16" s="7" t="n"/>
-      <c r="AE16" s="7" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>1.6/91</t>
+          <t>1.6/90</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 80 Ру 16</t>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 80 Ру 16</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>ГОСТ Р 52720-2007</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -2099,12 +2155,12 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>от -20 до +110</t>
+          <t>до + 110 °С</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>вода, воздух</t>
+          <t>теплоснабжение, горячий воздух (до 12 бар), питьевая горячая вода.</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -2124,7 +2180,7 @@
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>ручной (рукоятка)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="6" t="inlineStr">
@@ -2139,19 +2195,11 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Материал диска: высокопрочный чугун с эпоксидным покрытием; Уплотнение : резина EPDM</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M389</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr"/>
+      <c r="R17" s="6" t="inlineStr"/>
       <c r="S17" s="5" t="n">
         <v>1</v>
       </c>
@@ -2160,60 +2208,196 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U17" s="7" t="n"/>
-      <c r="V17" s="7" t="n"/>
-      <c r="W17" s="7" t="n"/>
-      <c r="X17" s="7" t="n"/>
-      <c r="Y17" s="7" t="n"/>
-      <c r="Z17" s="7" t="n"/>
-      <c r="AA17" s="8" t="n"/>
-      <c r="AB17" s="9">
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПТЛ FLN(w)-5-080-MR-HT Ду80 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="10">
         <f>AA17*S17</f>
         <v/>
       </c>
-      <c r="AC17" s="7" t="n"/>
-      <c r="AD17" s="7" t="n"/>
-      <c r="AE17" s="7" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="10" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="10" t="inlineStr"/>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr"/>
-      <c r="L18" s="10" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" s="10" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr"/>
-      <c r="P18" s="10" t="inlineStr"/>
-      <c r="Q18" s="10" t="inlineStr"/>
-      <c r="R18" s="10" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr"/>
-      <c r="T18" s="10" t="inlineStr"/>
-      <c r="U18" s="10" t="inlineStr"/>
-      <c r="V18" s="10" t="inlineStr"/>
-      <c r="W18" s="10" t="inlineStr"/>
-      <c r="X18" s="10" t="inlineStr"/>
-      <c r="Y18" s="10" t="inlineStr"/>
-      <c r="Z18" s="10" t="inlineStr"/>
-      <c r="AA18" s="10" t="inlineStr">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>1.6/91</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ГОСТ Р 52720-2007</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>от -20 до +110</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>вода, воздух</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>серый чугун GG25</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>межфланцевый</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>ручной (рукоятка)</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Материал диска: высокопрочный чугун с эпоксидным покрытием; Уплотнение : резина EPDM</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПВС FL(w)-3-080-MR-E Ду80 — Россия, ЗПВС в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="n"/>
+      <c r="Y18" s="8" t="n"/>
+      <c r="Z18" s="8" t="n"/>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="10">
+        <f>AA18*S18</f>
+        <v/>
+      </c>
+      <c r="AC18" s="8" t="n"/>
+      <c r="AD18" s="8" t="n"/>
+      <c r="AE18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="11" t="inlineStr"/>
+      <c r="B19" s="11" t="inlineStr"/>
+      <c r="C19" s="11" t="inlineStr"/>
+      <c r="D19" s="11" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr"/>
+      <c r="G19" s="11" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr"/>
+      <c r="O19" s="11" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr"/>
+      <c r="Q19" s="11" t="inlineStr"/>
+      <c r="R19" s="11" t="inlineStr"/>
+      <c r="S19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr"/>
+      <c r="U19" s="11" t="inlineStr"/>
+      <c r="V19" s="11" t="inlineStr"/>
+      <c r="W19" s="11" t="inlineStr"/>
+      <c r="X19" s="11" t="inlineStr"/>
+      <c r="Y19" s="11" t="inlineStr"/>
+      <c r="Z19" s="11" t="inlineStr"/>
+      <c r="AA19" s="11" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="AB18" s="11">
-        <f>SUM(AB5:AB17)</f>
+      <c r="AB19" s="12">
+        <f>SUM(AB6:AB18)</f>
         <v/>
       </c>
-      <c r="AC18" s="2" t="n"/>
-      <c r="AD18" s="2" t="n"/>
-      <c r="AE18" s="2" t="n"/>
+      <c r="AC19" s="2" t="n"/>
+      <c r="AD19" s="2" t="n"/>
+      <c r="AE19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/KAMCHATKA_ZAPOLNENIE/03_ООО_Торговый_Дом_АДЛ.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/03_ООО_Торговый_Дом_АДЛ.xlsx
@@ -933,7 +933,7 @@
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W6" s="7" t="inlineStr">
@@ -941,8 +941,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X6" s="8" t="n"/>
-      <c r="Y6" s="8" t="n"/>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>10357202</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
       <c r="Z6" s="8" t="n"/>
       <c r="AA6" s="9" t="n"/>
       <c r="AB6" s="10">
@@ -1041,7 +1049,7 @@
       </c>
       <c r="V7" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W7" s="7" t="inlineStr">
@@ -1049,8 +1057,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X7" s="8" t="n"/>
-      <c r="Y7" s="8" t="n"/>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>10357202</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
       <c r="Z7" s="8" t="n"/>
       <c r="AA7" s="9" t="n"/>
       <c r="AB7" s="10">
@@ -1149,7 +1165,7 @@
       </c>
       <c r="V8" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W8" s="7" t="inlineStr">
@@ -1157,8 +1173,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X8" s="8" t="n"/>
-      <c r="Y8" s="8" t="n"/>
+      <c r="X8" s="7" t="inlineStr">
+        <is>
+          <t>10837159</t>
+        </is>
+      </c>
+      <c r="Y8" s="7" t="inlineStr">
+        <is>
+          <t>13.07.2029</t>
+        </is>
+      </c>
       <c r="Z8" s="8" t="n"/>
       <c r="AA8" s="9" t="n"/>
       <c r="AB8" s="10">
@@ -1257,7 +1281,7 @@
       </c>
       <c r="V9" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W9" s="7" t="inlineStr">
@@ -1265,8 +1289,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X9" s="8" t="n"/>
-      <c r="Y9" s="8" t="n"/>
+      <c r="X9" s="7" t="inlineStr">
+        <is>
+          <t>10837159</t>
+        </is>
+      </c>
+      <c r="Y9" s="7" t="inlineStr">
+        <is>
+          <t>13.07.2029</t>
+        </is>
+      </c>
       <c r="Z9" s="8" t="n"/>
       <c r="AA9" s="9" t="n"/>
       <c r="AB9" s="10">
@@ -1365,7 +1397,7 @@
       </c>
       <c r="V10" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W10" s="7" t="inlineStr">
@@ -1373,8 +1405,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X10" s="8" t="n"/>
-      <c r="Y10" s="8" t="n"/>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>10357205</t>
+        </is>
+      </c>
+      <c r="Y10" s="7" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
       <c r="Z10" s="8" t="n"/>
       <c r="AA10" s="9" t="n"/>
       <c r="AB10" s="10">
@@ -1489,7 +1529,7 @@
       </c>
       <c r="V11" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W11" s="7" t="inlineStr">
@@ -1497,8 +1537,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X11" s="8" t="n"/>
-      <c r="Y11" s="8" t="n"/>
+      <c r="X11" s="7" t="inlineStr">
+        <is>
+          <t>10837159</t>
+        </is>
+      </c>
+      <c r="Y11" s="7" t="inlineStr">
+        <is>
+          <t>13.07.2029</t>
+        </is>
+      </c>
       <c r="Z11" s="8" t="n"/>
       <c r="AA11" s="9" t="n"/>
       <c r="AB11" s="10">
@@ -1613,7 +1661,7 @@
       </c>
       <c r="V12" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W12" s="7" t="inlineStr">
@@ -1621,8 +1669,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X12" s="8" t="n"/>
-      <c r="Y12" s="8" t="n"/>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>10837159</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>13.07.2029</t>
+        </is>
+      </c>
       <c r="Z12" s="8" t="n"/>
       <c r="AA12" s="9" t="n"/>
       <c r="AB12" s="10">
@@ -1737,7 +1793,7 @@
       </c>
       <c r="V13" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W13" s="7" t="inlineStr">
@@ -1745,8 +1801,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X13" s="8" t="n"/>
-      <c r="Y13" s="8" t="n"/>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>10357205</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
       <c r="Z13" s="8" t="n"/>
       <c r="AA13" s="9" t="n"/>
       <c r="AB13" s="10">
@@ -1857,7 +1921,7 @@
       </c>
       <c r="V14" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W14" s="7" t="inlineStr">
@@ -1865,8 +1929,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X14" s="8" t="n"/>
-      <c r="Y14" s="8" t="n"/>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>10357198</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
       <c r="Z14" s="8" t="n"/>
       <c r="AA14" s="9" t="n"/>
       <c r="AB14" s="10">
@@ -2099,7 +2171,7 @@
       </c>
       <c r="V16" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W16" s="7" t="inlineStr">
@@ -2107,8 +2179,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X16" s="8" t="n"/>
-      <c r="Y16" s="8" t="n"/>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>10357202</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
       <c r="Z16" s="8" t="n"/>
       <c r="AA16" s="9" t="n"/>
       <c r="AB16" s="10">
@@ -2215,7 +2295,7 @@
       </c>
       <c r="V17" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W17" s="7" t="inlineStr">
@@ -2223,8 +2303,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X17" s="8" t="n"/>
-      <c r="Y17" s="8" t="n"/>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>10357205</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
       <c r="Z17" s="8" t="n"/>
       <c r="AA17" s="9" t="n"/>
       <c r="AB17" s="10">
@@ -2339,7 +2427,7 @@
       </c>
       <c r="V18" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="W18" s="7" t="inlineStr">
@@ -2347,8 +2435,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X18" s="8" t="n"/>
-      <c r="Y18" s="8" t="n"/>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>10357205</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
       <c r="Z18" s="8" t="n"/>
       <c r="AA18" s="9" t="n"/>
       <c r="AB18" s="10">
